--- a/ods/db/resultados/Objetivo13.xlsx
+++ b/ods/db/resultados/Objetivo13.xlsx
@@ -4,17 +4,12 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Indicador 13.1.1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Indicador 13.1.2.a" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Indicador 13.1.2.b" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Indicador 13.1.2.c" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Indicador 13.1.2.d" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Indicador 13.1.2.e" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Indicador 13.1.3" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Indicador 13.2.2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Indicador 13.1.3" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Indicador 13.2.2" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9795,7 +9790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9838,17 +9833,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Indicador  13.1.2</t>
+          <t>Indicador  13.1.3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -9863,29 +9858,29 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10015</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2013</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Indicador  13.1.2</t>
+          <t>Indicador  13.1.3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -9900,29 +9895,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10015</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2017</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Indicador  13.1.2</t>
+          <t>Indicador  13.1.3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -9937,118 +9932,118 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10015</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2020</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Indicador  13.1.2</t>
+          <t>Indicador  13.1.3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Rondônia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10015</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2013</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Indicador  13.1.2</t>
+          <t>Indicador  13.1.3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Rondônia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10015</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2017</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Indicador  13.1.2</t>
+          <t>Indicador  13.1.3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Rondônia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10015</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -10060,37 +10055,2886 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Indicador  13.1.2</t>
+          <t>Indicador  13.1.3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Acre</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10015</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>36.4</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Acre</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>59.1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Acre</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>66.1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Roraima</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Roraima</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>33.3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Roraima</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Pará</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>30.6</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Pará</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>48.6</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Pará</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Amapá</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>43.8</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Amapá</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Amapá</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Tocantins</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Tocantins</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>15.8</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Tocantins</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Maranhão</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>12.4</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Maranhão</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Maranhão</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Piauí</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Piauí</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Piauí</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>23.4</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>41.3</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Rio Grande do Norte</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Rio Grande do Norte</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>28.1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Rio Grande do Norte</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Paraíba</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>10.8</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Paraíba</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>25.1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Paraíba</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>36.2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Pernambuco</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>32.4</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Pernambuco</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>55.7</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Pernambuco</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>30.4</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Alagoas</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>35.3</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Alagoas</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>53.9</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Alagoas</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>19.2</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Minas Gerais</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>32.4</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Minas Gerais</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Minas Gerais</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>67.9</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Espírito Santo</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>93.6</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Espírito Santo</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>93.6</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Espírito Santo</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>84.8</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>97.8</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>29.8</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>43.6</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Paraná</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Paraná</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>69.2</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Paraná</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Santa Catarina</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Santa Catarina</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Santa Catarina</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rio Grande do Sul</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>49.3</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Rio Grande do Sul</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>56.7</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Rio Grande do Sul</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Mato Grosso do Sul</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>49.4</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Mato Grosso do Sul</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Mato Grosso do Sul</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Mato Grosso</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Mato Grosso</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Mato Grosso</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>17.1</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Distrito Federal</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Distrito Federal</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Indicador  13.1.3</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Distrito Federal</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>9600</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2020</t>
         </is>
       </c>
     </row>
@@ -10105,4405 +12949,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID_INDICADOR</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CODG_UND_MED</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>VLR_VAR</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>CODG_UND_FED</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>DESC_UND_FED</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>CODG_VAR</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>CODG_ANO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>10100</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>10100</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>10100</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>10100</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>10100</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>10100</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>10100</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID_INDICADOR</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CODG_UND_MED</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>VLR_VAR</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>CODG_UND_FED</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>DESC_UND_FED</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>CODG_VAR</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>CODG_ANO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>10101</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>10101</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>10101</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>10101</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>10101</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>10101</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>10101</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID_INDICADOR</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CODG_UND_MED</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>VLR_VAR</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>CODG_UND_FED</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>DESC_UND_FED</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>CODG_VAR</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>CODG_ANO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>10102</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>10102</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>10102</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>10102</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>10102</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>10102</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>10102</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID_INDICADOR</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CODG_UND_MED</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>VLR_VAR</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>CODG_UND_FED</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>DESC_UND_FED</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>CODG_VAR</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>CODG_ANO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>10103</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>10103</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>10103</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>10103</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>10103</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>10103</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>10103</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G85"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID_INDICADOR</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CODG_UND_MED</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>VLR_VAR</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>CODG_UND_FED</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>DESC_UND_FED</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>CODG_VAR</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>CODG_ANO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>23.1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>33.8</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>47.0</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Rondônia</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Rondônia</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Rondônia</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>31.8</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Acre</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>36.4</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Acre</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>59.1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Acre</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>66.1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>75.8</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>26.7</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Roraima</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Roraima</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>33.3</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Roraima</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>17.4</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Pará</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>30.6</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Pará</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>48.6</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Pará</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>18.8</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Amapá</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>43.8</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Amapá</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Amapá</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Tocantins</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Tocantins</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>15.8</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Tocantins</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Maranhão</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>12.4</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Maranhão</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Maranhão</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Piauí</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Piauí</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>14.7</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Piauí</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>23.4</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Ceará</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>31.0</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Ceará</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>41.3</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Ceará</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Rio Grande do Norte</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Rio Grande do Norte</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>28.1</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Rio Grande do Norte</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Paraíba</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>10.8</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Paraíba</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>25.1</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Paraíba</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>36.2</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Pernambuco</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>32.4</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Pernambuco</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>55.7</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Pernambuco</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Alagoas</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>35.3</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Alagoas</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>53.9</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Alagoas</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>13.3</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Sergipe</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Sergipe</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Sergipe</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Bahia</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Bahia</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Bahia</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>26.7</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Minas Gerais</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>32.4</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Minas Gerais</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>48.5</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Minas Gerais</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>67.9</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Espírito Santo</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>93.6</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Espírito Santo</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>93.6</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Espírito Santo</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>84.8</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Rio de Janeiro</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Rio de Janeiro</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>97.8</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Rio de Janeiro</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>29.8</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>43.6</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>28.8</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Paraná</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Paraná</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>69.2</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Paraná</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Santa Catarina</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Santa Catarina</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>79.7</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Santa Catarina</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>23.1</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Rio Grande do Sul</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>49.3</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Rio Grande do Sul</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Rio Grande do Sul</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Mato Grosso do Sul</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>49.4</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Mato Grosso do Sul</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Mato Grosso do Sul</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Mato Grosso</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Mato Grosso</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>29.1</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Mato Grosso</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Goiás</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>12.6</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Goiás</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Goiás</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Distrito Federal</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Distrito Federal</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Indicador  13.1.3</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Distrito Federal</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:I187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
